--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4725274725274725</v>
+        <v>0.6385542168674698</v>
       </c>
       <c r="B2">
-        <v>0.02702702702702703</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4084507042253521</v>
+        <v>0.5571428571428572</v>
       </c>
       <c r="D2">
-        <v>0.65625</v>
+        <v>0.5391304347826087</v>
       </c>
       <c r="E2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -426,19 +426,19 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5571428571428572</v>
+        <v>0.5642857142857143</v>
       </c>
       <c r="D2">
-        <v>0.5391304347826087</v>
+        <v>0.5350877192982456</v>
       </c>
       <c r="E2">
         <v>83</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
